--- a/outputs/qa/batch-week1-aecn/Batch_INJ-06-2026-W1_QA_Checklist.xlsx
+++ b/outputs/qa/batch-week1-aecn/Batch_INJ-06-2026-W1_QA_Checklist.xlsx
@@ -2804,6 +2804,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -3302,9 +3303,10 @@
           <t>173.00 km</t>
         </is>
       </c>
-      <c r="E17" s="2">
-        <f> (1km)</f>
-        <v/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>= (1km)</t>
+        </is>
       </c>
     </row>
     <row r="18">
